--- a/Luban/Excel/事件对话.xlsx
+++ b/Luban/Excel/事件对话.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="86">
   <si>
     <t>节点id</t>
   </si>
@@ -2747,9 +2747,7 @@
       <c r="A41" s="5">
         <v>100038</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B41" s="5"/>
       <c r="D41" s="5"/>
       <c r="H41" s="5"/>
     </row>
@@ -2757,9 +2755,7 @@
       <c r="A42" s="5">
         <v>100039</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B42" s="5"/>
       <c r="D42" s="5"/>
       <c r="H42" s="5"/>
     </row>
@@ -2767,9 +2763,7 @@
       <c r="A43" s="5">
         <v>100040</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B43" s="5"/>
       <c r="D43" s="5"/>
       <c r="H43" s="5"/>
     </row>
@@ -2777,9 +2771,7 @@
       <c r="A44" s="5">
         <v>100041</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B44" s="5"/>
       <c r="D44" s="5"/>
       <c r="H44" s="5"/>
     </row>
@@ -2787,9 +2779,7 @@
       <c r="A45" s="5">
         <v>100042</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B45" s="5"/>
       <c r="D45" s="5"/>
       <c r="H45" s="5"/>
     </row>
@@ -2797,9 +2787,7 @@
       <c r="A46" s="5">
         <v>100043</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B46" s="5"/>
       <c r="D46" s="5"/>
       <c r="H46" s="5"/>
     </row>
@@ -2807,9 +2795,7 @@
       <c r="A47" s="5">
         <v>100044</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="D47" s="5"/>
       <c r="H47" s="5"/>
     </row>
@@ -2817,9 +2803,7 @@
       <c r="A48" s="5">
         <v>100045</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B48" s="5"/>
       <c r="D48" s="5"/>
       <c r="H48" s="5"/>
     </row>
@@ -2827,9 +2811,7 @@
       <c r="A49" s="5">
         <v>100046</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B49" s="5"/>
       <c r="D49" s="5"/>
       <c r="H49" s="5"/>
     </row>
@@ -2837,9 +2819,7 @@
       <c r="A50" s="5">
         <v>100047</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B50" s="5"/>
       <c r="D50" s="5"/>
       <c r="H50" s="5"/>
     </row>
@@ -2847,9 +2827,7 @@
       <c r="A51" s="5">
         <v>100048</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B51" s="5"/>
       <c r="D51" s="5"/>
       <c r="H51" s="5"/>
     </row>
@@ -2857,9 +2835,7 @@
       <c r="A52" s="5">
         <v>100049</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B52" s="5"/>
       <c r="D52" s="5"/>
       <c r="H52" s="5"/>
     </row>
@@ -2867,9 +2843,7 @@
       <c r="A53" s="5">
         <v>100050</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B53" s="5"/>
       <c r="D53" s="5"/>
       <c r="H53" s="5"/>
     </row>
